--- a/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
@@ -4431,7 +4431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -4449,6 +4449,7 @@
     <row r="2">
       <c r="I2" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -4494,11 +4495,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>DAYNITE</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>ELC_FIN_DEM</t>
@@ -4514,10 +4511,8 @@
           <t>FLO_SHAR</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2030,2035,2040,2045,2050</t>
-        </is>
+      <c r="F6" s="2" t="n">
+        <v>2030</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -4528,6 +4523,118 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ELC_FIN_DEM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ELC_GRID_RES</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FLO_SHAR</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LO</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
